--- a/human_resources_forms/009_ux_research_consent_form--human_resources_forms.xlsx
+++ b/human_resources_forms/009_ux_research_consent_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>participant_first_name</t>
+          <t>participant_first_name_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Participant First Name</t>
+          <t>Participant First Name 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>participant_last_name</t>
+          <t>participant_last_name_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Participant Last Name</t>
+          <t>Participant Last Name 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>participant_email</t>
+          <t>participant_email_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Participant Email</t>
+          <t>Participant Email 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>participant_phone</t>
+          <t>participant_phone_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Participant Phone</t>
+          <t>Participant Phone 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
